--- a/bansos.xlsx
+++ b/bansos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\fatha\Downloads\HTML\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{91E759C1-C84A-44DC-8DCF-C4DC593FC931}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{BC7D7E82-59D6-4CC9-B0D8-FF886620F6C4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="127" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="59">
   <si>
     <t>Nama</t>
   </si>
@@ -194,6 +194,9 @@
   </si>
   <si>
     <t>Dana Desa Tahap 2</t>
+  </si>
+  <si>
+    <t>Nik</t>
   </si>
 </sst>
 </file>
@@ -212,6 +215,7 @@
       <b/>
       <sz val="11"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="8"/>
@@ -233,7 +237,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -256,11 +260,22 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -274,12 +289,13 @@
     <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -582,7 +598,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H18"/>
+  <dimension ref="A1:I18"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
@@ -593,9 +609,10 @@
     <col min="6" max="6" width="17" customWidth="1"/>
     <col min="7" max="7" width="19" customWidth="1"/>
     <col min="8" max="8" width="34" customWidth="1"/>
+    <col min="9" max="9" width="24.54296875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -620,8 +637,11 @@
       <c r="H1" s="1" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I1" s="6" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A2" s="2" t="s">
         <v>8</v>
       </c>
@@ -646,12 +666,15 @@
       <c r="H2" s="2" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I2" s="7">
+        <v>317501101000</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A3" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="B3" s="6" t="s">
+      <c r="B3" s="5" t="s">
         <v>16</v>
       </c>
       <c r="C3" s="5" t="s">
@@ -672,8 +695,11 @@
       <c r="H3" s="2" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I3" s="7">
+        <v>317501101001</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A4" s="2" t="s">
         <v>22</v>
       </c>
@@ -698,8 +724,11 @@
       <c r="H4" s="2" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I4" s="7">
+        <v>317501101002</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A5" s="2" t="s">
         <v>26</v>
       </c>
@@ -724,8 +753,11 @@
       <c r="H5" s="2" t="s">
         <v>57</v>
       </c>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I5" s="7">
+        <v>317501101003</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A6" s="2" t="s">
         <v>28</v>
       </c>
@@ -750,8 +782,11 @@
       <c r="H6" s="2" t="s">
         <v>30</v>
       </c>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I6" s="7">
+        <v>317501101004</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A7" s="2" t="s">
         <v>31</v>
       </c>
@@ -776,8 +811,11 @@
       <c r="H7" s="2" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I7" s="7">
+        <v>317501101005</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A8" s="2" t="s">
         <v>34</v>
       </c>
@@ -802,8 +840,11 @@
       <c r="H8" s="2" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I8" s="7">
+        <v>317501101006</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A9" s="2" t="s">
         <v>39</v>
       </c>
@@ -828,8 +869,11 @@
       <c r="H9" s="2" t="s">
         <v>40</v>
       </c>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I9" s="7">
+        <v>317501101007</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A10" s="2" t="s">
         <v>41</v>
       </c>
@@ -854,8 +898,11 @@
       <c r="H10" s="2" t="s">
         <v>42</v>
       </c>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I10" s="7">
+        <v>317501101008</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A11" s="2" t="s">
         <v>43</v>
       </c>
@@ -880,8 +927,11 @@
       <c r="H11" s="2" t="s">
         <v>40</v>
       </c>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I11" s="7">
+        <v>317501101009</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A12" s="2" t="s">
         <v>44</v>
       </c>
@@ -906,8 +956,11 @@
       <c r="H12" s="2" t="s">
         <v>46</v>
       </c>
-    </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I12" s="7">
+        <v>317501101010</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A13" s="2" t="s">
         <v>47</v>
       </c>
@@ -932,8 +985,11 @@
       <c r="H13" s="2" t="s">
         <v>48</v>
       </c>
-    </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I13" s="7">
+        <v>317501101011</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A14" s="2" t="s">
         <v>49</v>
       </c>
@@ -958,8 +1014,11 @@
       <c r="H14" s="2" t="s">
         <v>50</v>
       </c>
-    </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I14" s="7">
+        <v>317501101012</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A15" s="2" t="s">
         <v>34</v>
       </c>
@@ -984,8 +1043,11 @@
       <c r="H15" s="2" t="s">
         <v>51</v>
       </c>
-    </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I15" s="7">
+        <v>317501101013</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A16" s="2" t="s">
         <v>52</v>
       </c>
@@ -1010,8 +1072,11 @@
       <c r="H16" s="2" t="s">
         <v>54</v>
       </c>
-    </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I16" s="7">
+        <v>317501101014</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A17" s="2" t="s">
         <v>55</v>
       </c>
@@ -1036,8 +1101,11 @@
       <c r="H17" s="2" t="s">
         <v>56</v>
       </c>
-    </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I17" s="7">
+        <v>317501101015</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A18" s="2" t="s">
         <v>55</v>
       </c>
@@ -1061,6 +1129,9 @@
       </c>
       <c r="H18" s="2" t="s">
         <v>57</v>
+      </c>
+      <c r="I18" s="7">
+        <v>317501101016</v>
       </c>
     </row>
   </sheetData>
